--- a/pathfinding_recordings.xlsx
+++ b/pathfinding_recordings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asmis\Documents\COMPSYS301_team2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC71BDC4-2B76-4AB4-8C20-AA3E22B81A94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31B54BB8-F766-4D89-8287-E6B0C8C33FFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{7700CBF5-08F8-4E5E-A6C4-5AD761BAA852}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="15">
   <si>
     <t>algorithm</t>
   </si>
@@ -76,6 +76,15 @@
   </si>
   <si>
     <t>Dijkstras</t>
+  </si>
+  <si>
+    <t>A*</t>
+  </si>
+  <si>
+    <t>BFS</t>
+  </si>
+  <si>
+    <t>GBF</t>
   </si>
 </sst>
 </file>
@@ -447,7 +456,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CCF085A-D1B2-4377-B6BE-870B791A9AB1}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
@@ -533,6 +542,114 @@
         <v>8</v>
       </c>
       <c r="D7">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B15" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16">
         <v>77</v>
       </c>
     </row>
@@ -543,7 +660,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC9C14E6-257F-483B-AFD0-26ADBB495A4C}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
@@ -632,6 +749,114 @@
         <v>26</v>
       </c>
     </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B15" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pathfinding_recordings.xlsx
+++ b/pathfinding_recordings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asmis\Documents\COMPSYS301_team2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31B54BB8-F766-4D89-8287-E6B0C8C33FFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77599F85-7738-4697-9E3A-9F78BCE3F05A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{7700CBF5-08F8-4E5E-A6C4-5AD761BAA852}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="17">
   <si>
     <t>algorithm</t>
   </si>
@@ -85,6 +85,12 @@
   </si>
   <si>
     <t>GBF</t>
+  </si>
+  <si>
+    <t>floodfill</t>
+  </si>
+  <si>
+    <t>[14,8]</t>
   </si>
 </sst>
 </file>
@@ -456,7 +462,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CCF085A-D1B2-4377-B6BE-870B791A9AB1}">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
@@ -650,6 +656,42 @@
         <v>8</v>
       </c>
       <c r="D16">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19">
         <v>77</v>
       </c>
     </row>
@@ -660,7 +702,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC9C14E6-257F-483B-AFD0-26ADBB495A4C}">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
@@ -857,6 +899,42 @@
         <v>26</v>
       </c>
     </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pathfinding_recordings.xlsx
+++ b/pathfinding_recordings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asmis\Documents\COMPSYS301_team2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/madi/Desktop/COMPSYS301_team2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77599F85-7738-4697-9E3A-9F78BCE3F05A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37E239C7-D950-784B-B1B3-875082C621C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{7700CBF5-08F8-4E5E-A6C4-5AD761BAA852}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{7700CBF5-08F8-4E5E-A6C4-5AD761BAA852}"/>
   </bookViews>
   <sheets>
     <sheet name="map1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="17">
   <si>
     <t>algorithm</t>
   </si>
@@ -90,7 +90,7 @@
     <t>floodfill</t>
   </si>
   <si>
-    <t>[14,8]</t>
+    <t>Dynamic A*</t>
   </si>
 </sst>
 </file>
@@ -126,8 +126,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -462,10 +468,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CCF085A-D1B2-4377-B6BE-870B791A9AB1}">
-  <dimension ref="A1:D19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -479,8 +485,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B2" t="s">
@@ -493,7 +499,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="1"/>
       <c r="B3" t="s">
         <v>5</v>
       </c>
@@ -504,7 +511,8 @@
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="1"/>
       <c r="B4" t="s">
         <v>5</v>
       </c>
@@ -515,8 +523,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B5" t="s">
@@ -529,7 +537,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="1"/>
       <c r="B6" t="s">
         <v>5</v>
       </c>
@@ -540,7 +549,8 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="1"/>
       <c r="B7" t="s">
         <v>5</v>
       </c>
@@ -551,8 +561,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B8" t="s">
@@ -565,7 +575,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="1"/>
       <c r="B9" t="s">
         <v>5</v>
       </c>
@@ -576,7 +587,8 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="1"/>
       <c r="B10" t="s">
         <v>5</v>
       </c>
@@ -587,8 +599,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B11" t="s">
@@ -601,7 +613,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="1"/>
       <c r="B12" t="s">
         <v>5</v>
       </c>
@@ -612,7 +625,8 @@
         <v>51</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="1"/>
       <c r="B13" t="s">
         <v>5</v>
       </c>
@@ -623,8 +637,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B14" t="s">
@@ -637,7 +651,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" s="1"/>
       <c r="B15" t="s">
         <v>5</v>
       </c>
@@ -648,7 +663,8 @@
         <v>51</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="1"/>
       <c r="B16" t="s">
         <v>5</v>
       </c>
@@ -659,21 +675,22 @@
         <v>77</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B17" t="s">
         <v>5</v>
       </c>
       <c r="C17" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D17">
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="1"/>
       <c r="B18" t="s">
         <v>5</v>
       </c>
@@ -684,7 +701,8 @@
         <v>51</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="1"/>
       <c r="B19" t="s">
         <v>5</v>
       </c>
@@ -695,17 +713,65 @@
         <v>77</v>
       </c>
     </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="2"/>
+      <c r="B21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="2"/>
+      <c r="B22" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22">
+        <v>77</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A17:A19"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC9C14E6-257F-483B-AFD0-26ADBB495A4C}">
-  <dimension ref="A1:D19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -719,8 +785,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B2" t="s">
@@ -733,7 +799,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="1"/>
       <c r="B3" t="s">
         <v>5</v>
       </c>
@@ -744,7 +811,8 @@
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="1"/>
       <c r="B4" t="s">
         <v>5</v>
       </c>
@@ -755,8 +823,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B5" t="s">
@@ -769,7 +837,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="1"/>
       <c r="B6" t="s">
         <v>5</v>
       </c>
@@ -780,7 +849,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="1"/>
       <c r="B7" t="s">
         <v>5</v>
       </c>
@@ -791,8 +861,8 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B8" t="s">
@@ -805,7 +875,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="1"/>
       <c r="B9" t="s">
         <v>5</v>
       </c>
@@ -816,7 +887,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="1"/>
       <c r="B10" t="s">
         <v>5</v>
       </c>
@@ -827,8 +899,8 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B11" t="s">
@@ -841,7 +913,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="1"/>
       <c r="B12" t="s">
         <v>5</v>
       </c>
@@ -852,7 +925,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="1"/>
       <c r="B13" t="s">
         <v>5</v>
       </c>
@@ -863,8 +937,8 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B14" t="s">
@@ -877,7 +951,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" s="1"/>
       <c r="B15" t="s">
         <v>5</v>
       </c>
@@ -888,7 +963,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="1"/>
       <c r="B16" t="s">
         <v>5</v>
       </c>
@@ -899,8 +975,8 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B17" t="s">
@@ -913,7 +989,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="1"/>
       <c r="B18" t="s">
         <v>5</v>
       </c>
@@ -924,7 +1001,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="1"/>
       <c r="B19" t="s">
         <v>5</v>
       </c>
@@ -935,7 +1013,54 @@
         <v>26</v>
       </c>
     </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="2"/>
+      <c r="B21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="2"/>
+      <c r="B22" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A17:A19"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/pathfinding_recordings.xlsx
+++ b/pathfinding_recordings.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/madi/Desktop/COMPSYS301_team2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asmis\Documents\COMPSYS301_team2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37E239C7-D950-784B-B1B3-875082C621C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A697C0E9-2B55-49BF-8A79-5004856E7AF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{7700CBF5-08F8-4E5E-A6C4-5AD761BAA852}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{7700CBF5-08F8-4E5E-A6C4-5AD761BAA852}"/>
   </bookViews>
   <sheets>
     <sheet name="map1" sheetId="1" r:id="rId1"/>
     <sheet name="map8" sheetId="2" r:id="rId2"/>
+    <sheet name="map30" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="20">
   <si>
     <t>algorithm</t>
   </si>
@@ -91,6 +92,15 @@
   </si>
   <si>
     <t>Dynamic A*</t>
+  </si>
+  <si>
+    <t>[2,12]</t>
+  </si>
+  <si>
+    <t>[4,8]</t>
+  </si>
+  <si>
+    <t>[10,16]</t>
   </si>
 </sst>
 </file>
@@ -129,10 +139,10 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -469,9 +479,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CCF085A-D1B2-4377-B6BE-870B791A9AB1}">
   <dimension ref="A1:D22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -485,8 +495,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B2" t="s">
@@ -499,8 +509,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="1"/>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="2"/>
       <c r="B3" t="s">
         <v>5</v>
       </c>
@@ -511,8 +521,8 @@
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="1"/>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="2"/>
       <c r="B4" t="s">
         <v>5</v>
       </c>
@@ -523,8 +533,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B5" t="s">
@@ -537,8 +547,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="1"/>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="2"/>
       <c r="B6" t="s">
         <v>5</v>
       </c>
@@ -549,8 +559,8 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="1"/>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="2"/>
       <c r="B7" t="s">
         <v>5</v>
       </c>
@@ -561,8 +571,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B8" t="s">
@@ -575,8 +585,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="1"/>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="2"/>
       <c r="B9" t="s">
         <v>5</v>
       </c>
@@ -587,8 +597,8 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="1"/>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="2"/>
       <c r="B10" t="s">
         <v>5</v>
       </c>
@@ -599,8 +609,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B11" t="s">
@@ -613,8 +623,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="1"/>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="2"/>
       <c r="B12" t="s">
         <v>5</v>
       </c>
@@ -625,8 +635,8 @@
         <v>51</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="1"/>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="2"/>
       <c r="B13" t="s">
         <v>5</v>
       </c>
@@ -637,8 +647,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B14" t="s">
@@ -651,8 +661,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="1"/>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="2"/>
       <c r="B15" t="s">
         <v>5</v>
       </c>
@@ -663,8 +673,8 @@
         <v>51</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="1"/>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" s="2"/>
       <c r="B16" t="s">
         <v>5</v>
       </c>
@@ -675,8 +685,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B17" t="s">
@@ -689,8 +699,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="1"/>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="2"/>
       <c r="B18" t="s">
         <v>5</v>
       </c>
@@ -701,8 +711,8 @@
         <v>51</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="1"/>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="2"/>
       <c r="B19" t="s">
         <v>5</v>
       </c>
@@ -713,8 +723,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="2" t="s">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B20" t="s">
@@ -727,8 +737,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="2"/>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="1"/>
       <c r="B21" t="s">
         <v>5</v>
       </c>
@@ -739,8 +749,8 @@
         <v>51</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="2"/>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="1"/>
       <c r="B22" t="s">
         <v>5</v>
       </c>
@@ -769,9 +779,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC9C14E6-257F-483B-AFD0-26ADBB495A4C}">
   <dimension ref="A1:D22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -785,8 +795,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B2" t="s">
@@ -799,8 +809,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="1"/>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="2"/>
       <c r="B3" t="s">
         <v>5</v>
       </c>
@@ -811,8 +821,8 @@
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="1"/>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="2"/>
       <c r="B4" t="s">
         <v>5</v>
       </c>
@@ -823,8 +833,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B5" t="s">
@@ -837,8 +847,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="1"/>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="2"/>
       <c r="B6" t="s">
         <v>5</v>
       </c>
@@ -849,8 +859,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="1"/>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="2"/>
       <c r="B7" t="s">
         <v>5</v>
       </c>
@@ -861,8 +871,8 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B8" t="s">
@@ -875,8 +885,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="1"/>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="2"/>
       <c r="B9" t="s">
         <v>5</v>
       </c>
@@ -887,8 +897,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="1"/>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="2"/>
       <c r="B10" t="s">
         <v>5</v>
       </c>
@@ -899,8 +909,8 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B11" t="s">
@@ -913,8 +923,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="1"/>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="2"/>
       <c r="B12" t="s">
         <v>5</v>
       </c>
@@ -925,8 +935,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="1"/>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="2"/>
       <c r="B13" t="s">
         <v>5</v>
       </c>
@@ -937,8 +947,8 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B14" t="s">
@@ -951,8 +961,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="1"/>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="2"/>
       <c r="B15" t="s">
         <v>5</v>
       </c>
@@ -963,8 +973,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="1"/>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" s="2"/>
       <c r="B16" t="s">
         <v>5</v>
       </c>
@@ -975,8 +985,8 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B17" t="s">
@@ -989,8 +999,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="1"/>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="2"/>
       <c r="B18" t="s">
         <v>5</v>
       </c>
@@ -1001,8 +1011,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="1"/>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="2"/>
       <c r="B19" t="s">
         <v>5</v>
       </c>
@@ -1013,8 +1023,8 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="2" t="s">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B20" t="s">
@@ -1027,8 +1037,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="2"/>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="1"/>
       <c r="B21" t="s">
         <v>5</v>
       </c>
@@ -1039,8 +1049,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="2"/>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="1"/>
       <c r="B22" t="s">
         <v>5</v>
       </c>
@@ -1049,6 +1059,305 @@
       </c>
       <c r="D22">
         <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A17:A19"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9874D156-B2E6-437E-BEDE-F85878E12C33}">
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="2"/>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="2"/>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="2"/>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="2"/>
+      <c r="B7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="2"/>
+      <c r="B9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="2"/>
+      <c r="B10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="2"/>
+      <c r="B12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="2"/>
+      <c r="B13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="2"/>
+      <c r="B15" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" s="2"/>
+      <c r="B16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="2"/>
+      <c r="B18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="2"/>
+      <c r="B19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="1"/>
+      <c r="B21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="1"/>
+      <c r="B22" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
